--- a/Excel/WorldConfig.xlsx
+++ b/Excel/WorldConfig.xlsx
@@ -59,7 +59,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>穷奇</t>
+    <t>青龙</t>
   </si>
   <si>
     <t>5,9,5,9,15,5,5,15</t>
@@ -74,16 +74,16 @@
     <t>无敌</t>
   </si>
   <si>
-    <t>饕餮</t>
-  </si>
-  <si>
-    <t>梼杌</t>
+    <t>白虎</t>
+  </si>
+  <si>
+    <t>朱雀</t>
   </si>
   <si>
     <t>10,600,60,30,200,10,2,6</t>
   </si>
   <si>
-    <t>混沌</t>
+    <t>玄武</t>
   </si>
 </sst>
 </file>
@@ -96,7 +96,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,12 +136,6 @@
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -613,137 +607,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -758,7 +752,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -1200,13 +1193,13 @@
       <c r="D6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="9" t="s">
         <v>13</v>
       </c>
       <c r="H6" s="1" t="s">
@@ -1220,13 +1213,13 @@
       <c r="D7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="9" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="1" t="s">
@@ -1240,13 +1233,13 @@
       <c r="D8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="1" t="s">
@@ -1257,16 +1250,16 @@
       <c r="C9" s="6">
         <v>4</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="9" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="1" t="s">

--- a/Excel/WorldConfig.xlsx
+++ b/Excel/WorldConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
   <si>
     <t>ID</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>无敌</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>白虎</t>
@@ -1206,12 +1209,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="C7" s="6">
         <v>2</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>11</v>
@@ -1226,12 +1235,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="C8" s="6">
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>11</v>
@@ -1240,18 +1255,24 @@
         <v>12</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="C9" s="6">
         <v>4</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>11</v>
@@ -1260,7 +1281,7 @@
         <v>12</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>14</v>

--- a/Excel/WorldConfig.xlsx
+++ b/Excel/WorldConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>ID</t>
   </si>
@@ -35,16 +35,7 @@
     <t>MapName</t>
   </si>
   <si>
-    <t>ItemType</t>
-  </si>
-  <si>
-    <t>ItemIdList</t>
-  </si>
-  <si>
-    <t>ItemQuantity</t>
-  </si>
-  <si>
-    <t>Desc</t>
+    <t>Cycle</t>
   </si>
   <si>
     <t>Id</t>
@@ -56,34 +47,16 @@
     <t>string</t>
   </si>
   <si>
-    <t>int[]</t>
-  </si>
-  <si>
     <t>青龙</t>
   </si>
   <si>
-    <t>5,9,5,9,15,5,5,15</t>
-  </si>
-  <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020</t>
-  </si>
-  <si>
-    <t>10,500,50,25,100,5,1,5</t>
-  </si>
-  <si>
-    <t>无敌</t>
+    <t>白虎</t>
   </si>
   <si>
     <t>#</t>
   </si>
   <si>
-    <t>白虎</t>
-  </si>
-  <si>
     <t>朱雀</t>
-  </si>
-  <si>
-    <t>10,600,60,30,200,10,2,6</t>
   </si>
   <si>
     <t>玄武</t>
@@ -740,7 +713,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -750,13 +723,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1076,45 +1044,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K93"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <dimension ref="A1:H93"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="20.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="13.25" style="2" customWidth="1"/>
-    <col min="11" max="11" width="9.625" style="2" customWidth="1"/>
-    <col min="12" max="16373" width="9" style="2"/>
-    <col min="16374" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.1238938053097" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.3716814159292" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.2477876106195" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.6283185840708" style="2" customWidth="1"/>
+    <col min="9" max="16370" width="9" style="2"/>
+    <col min="16371" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1126,24 +1084,15 @@
       <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="2"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="2"/>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
@@ -1151,140 +1100,80 @@
       <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="2"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="2"/>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:5">
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:5">
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E7" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="E8" s="6">
         <v>8</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C6" s="6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6" t="s">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="6">
-        <v>2</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="6">
-        <v>3</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="6">
-        <v>4</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>14</v>
+      <c r="E9" s="6">
+        <v>10</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1"/>
@@ -1373,7 +1262,7 @@
     <row r="93" s="1" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5 H3:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 F3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/WorldConfig.xlsx
+++ b/Excel/WorldConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>ID</t>
   </si>
@@ -53,10 +53,10 @@
     <t>白虎</t>
   </si>
   <si>
-    <t>#</t>
+    <t>朱雀</t>
   </si>
   <si>
-    <t>朱雀</t>
+    <t>#</t>
   </si>
   <si>
     <t>玄武</t>
@@ -1142,18 +1142,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:5">
       <c r="C8" s="5">
         <v>3</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="6">
         <v>8</v>
@@ -1161,10 +1155,10 @@
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="5">
         <v>4</v>
@@ -1262,7 +1256,7 @@
     <row r="93" s="1" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 F3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/WorldConfig.xlsx
+++ b/Excel/WorldConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>ID</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>朱雀</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>玄武</t>
@@ -1047,13 +1044,13 @@
   <dimension ref="A1:H93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.1238938053097" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.3716814159292" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.2477876106195" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.6283185840708" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.625" style="2" customWidth="1"/>
     <col min="9" max="16370" width="9" style="2"/>
     <col min="16371" max="16384" width="9" style="1"/>
   </cols>
@@ -1153,18 +1150,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:5">
       <c r="C9" s="5">
         <v>4</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="6">
         <v>10</v>

--- a/Excel/WorldConfig.xlsx
+++ b/Excel/WorldConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>ID</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>玄武</t>
+  </si>
+  <si>
+    <t>麒麟</t>
   </si>
 </sst>
 </file>
@@ -1117,7 +1120,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:5">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C6" s="5">
         <v>1</v>
       </c>
@@ -1128,7 +1131,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:5">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C7" s="5">
         <v>2</v>
       </c>
@@ -1139,7 +1142,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:5">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C8" s="5">
         <v>3</v>
       </c>
@@ -1150,7 +1153,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:5">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C9" s="5">
         <v>4</v>
       </c>
@@ -1161,7 +1164,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1"/>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1">
+        <v>15</v>
+      </c>
+    </row>
     <row r="11" s="1" customFormat="1" customHeight="1"/>
     <row r="12" s="1" customFormat="1" customHeight="1"/>
     <row r="13" s="1" customFormat="1" customHeight="1"/>

--- a/Excel/WorldConfig.xlsx
+++ b/Excel/WorldConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>ID</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>麒麟</t>
+  </si>
+  <si>
+    <t>极青龙</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +1178,17 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1"/>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="1">
+        <v>20</v>
+      </c>
+    </row>
     <row r="12" s="1" customFormat="1" customHeight="1"/>
     <row r="13" s="1" customFormat="1" customHeight="1"/>
     <row r="14" s="1" customFormat="1" customHeight="1"/>

--- a/Excel/WorldConfig.xlsx
+++ b/Excel/WorldConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>ID</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>极青龙</t>
+  </si>
+  <si>
+    <t>极白虎</t>
   </si>
 </sst>
 </file>
@@ -1189,7 +1192,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1"/>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1">
+        <v>23</v>
+      </c>
+    </row>
     <row r="13" s="1" customFormat="1" customHeight="1"/>
     <row r="14" s="1" customFormat="1" customHeight="1"/>
     <row r="15" s="1" customFormat="1" customHeight="1"/>

--- a/Excel/WorldConfig.xlsx
+++ b/Excel/WorldConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>ID</t>
   </si>
@@ -66,6 +71,9 @@
   </si>
   <si>
     <t>极白虎</t>
+  </si>
+  <si>
+    <t>极朱雀</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1211,17 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1"/>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1">
+        <v>26</v>
+      </c>
+    </row>
     <row r="14" s="1" customFormat="1" customHeight="1"/>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
     <row r="16" s="1" customFormat="1" customHeight="1"/>
